--- a/data/trans_orig/IBSE_100-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IBSE_100-Estudios-trans_orig.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>69,33</t>
+          <t>69,49</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,81</t>
+          <t>65,91</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,44; 71,07</t>
+          <t>67,8; 71,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,24; 64,65</t>
+          <t>62,16; 64,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,74; 66,83</t>
+          <t>64,93; 66,88</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80,27</t>
+          <t>79,28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,9</t>
+          <t>76,15</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78,6</t>
+          <t>77,73</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,07; 82,78</t>
+          <t>78,52; 80,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,01; 78,22</t>
+          <t>75,44; 76,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,7; 80,31</t>
+          <t>77,18; 78,27</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,7</t>
+          <t>80,76</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,88</t>
+          <t>79,91</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,1; 82,04</t>
+          <t>79,27; 82,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,91; 80,07</t>
+          <t>78,07; 80,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,0; 80,72</t>
+          <t>78,99; 80,8</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,74</t>
+          <t>78,01</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,57</t>
+          <t>73,98</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76,6</t>
+          <t>75,94</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,73; 80,89</t>
+          <t>77,36; 78,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,74; 75,65</t>
+          <t>73,43; 74,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,94; 78,07</t>
+          <t>75,53; 76,41</t>
         </is>
       </c>
     </row>
